--- a/data/desempeno/kpi_desempeno_2026-03-03.xlsx
+++ b/data/desempeno/kpi_desempeno_2026-03-03.xlsx
@@ -415,16 +415,16 @@
         <v>131</v>
       </c>
       <c r="F7" s="65">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7" s="65">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="H7" s="65">
         <v>0</v>
       </c>
       <c r="I7" s="64">
-        <v>2103.00</v>
+        <v>2104.00</v>
       </c>
     </row>
     <row r="8">
@@ -1128,22 +1128,22 @@
         <v>1924</v>
       </c>
       <c r="F30" s="69">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G30" s="69">
-        <v>34569</v>
+        <v>34570</v>
       </c>
       <c r="H30" s="69">
         <v>0</v>
       </c>
       <c r="I30" s="69">
-        <v>1279.33</v>
+        <v>1279.37</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31" s="0">
         <is>
-          <t xml:space="preserve">Reporte generado: 09-03-2026 07:03 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 11-03-2026 08:29 a. m. </t>
         </is>
       </c>
     </row>
